--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128387626</v>
       </c>
       <c r="B2" t="n">
-        <v>91323</v>
+        <v>91325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128387495</v>
+        <v>128387693</v>
       </c>
       <c r="B5" t="n">
-        <v>82873</v>
+        <v>92057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774641</v>
+        <v>774735</v>
       </c>
       <c r="R5" t="n">
-        <v>7156263</v>
+        <v>7156256</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,11 +1071,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128387693</v>
+        <v>128387495</v>
       </c>
       <c r="B6" t="n">
-        <v>92055</v>
+        <v>82873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1145,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774735</v>
+        <v>774641</v>
       </c>
       <c r="R6" t="n">
-        <v>7156256</v>
+        <v>7156263</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,6 +1176,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128387626</v>
       </c>
       <c r="B2" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128387579</v>
       </c>
       <c r="B3" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128387506</v>
+        <v>128387693</v>
       </c>
       <c r="B4" t="n">
-        <v>4779</v>
+        <v>92149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,28 +901,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774639</v>
+        <v>774735</v>
       </c>
       <c r="R4" t="n">
-        <v>7156269</v>
+        <v>7156256</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128387693</v>
+        <v>128387495</v>
       </c>
       <c r="B5" t="n">
-        <v>92057</v>
+        <v>82942</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774735</v>
+        <v>774641</v>
       </c>
       <c r="R5" t="n">
-        <v>7156256</v>
+        <v>7156263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128387495</v>
+        <v>128387697</v>
       </c>
       <c r="B6" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774641</v>
+        <v>774735</v>
       </c>
       <c r="R6" t="n">
-        <v>7156263</v>
+        <v>7156256</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,11 +1183,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,41 +1210,39 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128387697</v>
+        <v>128387506</v>
       </c>
       <c r="B7" t="n">
-        <v>82873</v>
+        <v>4779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>774735</v>
+        <v>774639</v>
       </c>
       <c r="R7" t="n">
-        <v>7156256</v>
+        <v>7156269</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -890,32 +890,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128387693</v>
+        <v>128387495</v>
       </c>
       <c r="B4" t="n">
-        <v>92149</v>
+        <v>82942</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774735</v>
+        <v>774641</v>
       </c>
       <c r="R4" t="n">
-        <v>7156256</v>
+        <v>7156263</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128387495</v>
+        <v>128387693</v>
       </c>
       <c r="B5" t="n">
-        <v>82942</v>
+        <v>92149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774641</v>
+        <v>774735</v>
       </c>
       <c r="R5" t="n">
-        <v>7156263</v>
+        <v>7156256</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,11 +1078,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128387626</v>
       </c>
       <c r="B2" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128387579</v>
       </c>
       <c r="B3" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,32 +890,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128387495</v>
+        <v>128387693</v>
       </c>
       <c r="B4" t="n">
-        <v>82942</v>
+        <v>92161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774641</v>
+        <v>774735</v>
       </c>
       <c r="R4" t="n">
-        <v>7156263</v>
+        <v>7156256</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128387693</v>
+        <v>128387495</v>
       </c>
       <c r="B5" t="n">
-        <v>92149</v>
+        <v>82946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774735</v>
+        <v>774641</v>
       </c>
       <c r="R5" t="n">
-        <v>7156256</v>
+        <v>7156263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1108,7 @@
         <v>128387697</v>
       </c>
       <c r="B6" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128387626</v>
       </c>
       <c r="B2" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128387579</v>
       </c>
       <c r="B3" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128387693</v>
       </c>
       <c r="B4" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>128387495</v>
       </c>
       <c r="B5" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>128387697</v>
       </c>
       <c r="B6" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -890,32 +890,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128387693</v>
+        <v>128387495</v>
       </c>
       <c r="B4" t="n">
-        <v>92163</v>
+        <v>82948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774735</v>
+        <v>774641</v>
       </c>
       <c r="R4" t="n">
-        <v>7156256</v>
+        <v>7156263</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128387495</v>
+        <v>128387693</v>
       </c>
       <c r="B5" t="n">
-        <v>82948</v>
+        <v>92163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774641</v>
+        <v>774735</v>
       </c>
       <c r="R5" t="n">
-        <v>7156263</v>
+        <v>7156256</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,11 +1078,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128387626</v>
       </c>
       <c r="B2" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>128387693</v>
       </c>
       <c r="B5" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128387626</v>
       </c>
       <c r="B2" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128387579</v>
       </c>
       <c r="B3" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,32 +890,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128387495</v>
+        <v>128387693</v>
       </c>
       <c r="B4" t="n">
-        <v>82948</v>
+        <v>92191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774641</v>
+        <v>774735</v>
       </c>
       <c r="R4" t="n">
-        <v>7156263</v>
+        <v>7156256</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128387693</v>
+        <v>128387495</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>82975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774735</v>
+        <v>774641</v>
       </c>
       <c r="R5" t="n">
-        <v>7156256</v>
+        <v>7156263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1108,7 @@
         <v>128387697</v>
       </c>
       <c r="B6" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -890,32 +890,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128387693</v>
+        <v>128387495</v>
       </c>
       <c r="B4" t="n">
-        <v>92191</v>
+        <v>82975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774735</v>
+        <v>774641</v>
       </c>
       <c r="R4" t="n">
-        <v>7156256</v>
+        <v>7156263</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128387495</v>
+        <v>128387693</v>
       </c>
       <c r="B5" t="n">
-        <v>82975</v>
+        <v>92191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774641</v>
+        <v>774735</v>
       </c>
       <c r="R5" t="n">
-        <v>7156263</v>
+        <v>7156256</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,11 +1078,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128387626</v>
       </c>
       <c r="B2" t="n">
-        <v>91459</v>
+        <v>91469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128387579</v>
       </c>
       <c r="B3" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128387495</v>
       </c>
       <c r="B4" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>128387693</v>
       </c>
       <c r="B5" t="n">
-        <v>92191</v>
+        <v>92201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>128387697</v>
       </c>
       <c r="B6" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128387626</v>
       </c>
       <c r="B2" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128387579</v>
       </c>
       <c r="B3" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,32 +890,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128387495</v>
+        <v>128387693</v>
       </c>
       <c r="B4" t="n">
-        <v>82979</v>
+        <v>92205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774641</v>
+        <v>774735</v>
       </c>
       <c r="R4" t="n">
-        <v>7156263</v>
+        <v>7156256</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128387693</v>
+        <v>128387495</v>
       </c>
       <c r="B5" t="n">
-        <v>92201</v>
+        <v>82983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774735</v>
+        <v>774641</v>
       </c>
       <c r="R5" t="n">
-        <v>7156256</v>
+        <v>7156263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1108,7 @@
         <v>128387697</v>
       </c>
       <c r="B6" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -890,32 +890,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128387693</v>
+        <v>128387495</v>
       </c>
       <c r="B4" t="n">
-        <v>92205</v>
+        <v>82983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774735</v>
+        <v>774641</v>
       </c>
       <c r="R4" t="n">
-        <v>7156256</v>
+        <v>7156263</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128387495</v>
+        <v>128387693</v>
       </c>
       <c r="B5" t="n">
-        <v>82983</v>
+        <v>92205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774641</v>
+        <v>774735</v>
       </c>
       <c r="R5" t="n">
-        <v>7156263</v>
+        <v>7156256</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,11 +1078,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128387626</v>
       </c>
       <c r="B2" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128387579</v>
       </c>
       <c r="B3" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128387495</v>
       </c>
       <c r="B4" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>128387693</v>
       </c>
       <c r="B5" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>128387697</v>
       </c>
       <c r="B6" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -1292,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">

--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128387626</v>
+        <v>204540</v>
       </c>
       <c r="B2" t="n">
-        <v>91478</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storberget, Vb</t>
+          <t>Väster om Storberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>774698</v>
+        <v>774708</v>
       </c>
       <c r="R2" t="n">
-        <v>7156298</v>
+        <v>7156248</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128387579</v>
+        <v>378698</v>
       </c>
       <c r="B3" t="n">
-        <v>82892</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,26 +801,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storberget, Vb</t>
+          <t>Väster om Storberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774670</v>
+        <v>774708</v>
       </c>
       <c r="R3" t="n">
-        <v>7156298</v>
+        <v>7156248</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på stammen av en gammal gran</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128387495</v>
+        <v>128387438</v>
       </c>
       <c r="B4" t="n">
-        <v>82892</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,10 +911,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774641</v>
+        <v>774630</v>
       </c>
       <c r="R4" t="n">
-        <v>7156263</v>
+        <v>7156243</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +951,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
+          <t>på stammen av en gammal gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,32 +979,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128387693</v>
+        <v>128387495</v>
       </c>
       <c r="B5" t="n">
-        <v>92210</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774735</v>
+        <v>774641</v>
       </c>
       <c r="R5" t="n">
-        <v>7156256</v>
+        <v>7156263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på stammen av gammal senvuxen gran inne i avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128387697</v>
+        <v>128387579</v>
       </c>
       <c r="B6" t="n">
-        <v>82892</v>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774735</v>
+        <v>774670</v>
       </c>
       <c r="R6" t="n">
-        <v>7156256</v>
+        <v>7156298</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,6 +1167,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på stammen av en gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,39 +1199,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128387506</v>
+        <v>128387697</v>
       </c>
       <c r="B7" t="n">
-        <v>4779</v>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1250,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>774639</v>
+        <v>774735</v>
       </c>
       <c r="R7" t="n">
-        <v>7156269</v>
+        <v>7156256</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
@@ -1310,6 +1301,1166 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128387693</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>774735</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7156256</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128387370</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>774653</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7156319</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128387626</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>774698</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7156298</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1852569</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Väster om Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>774708</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7156248</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2005-12-31</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128387379</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>774626</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7156298</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1951388</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Väster om Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>774708</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7156248</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2005-12-31</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128387390</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>774621</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7156289</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på grov gammal sälg</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128387506</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>774639</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7156269</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128388130</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>774651</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7156324</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128388139</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>774621</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7156288</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ca 1 x 2 meter med bladrosetter ca 10 meter från gränsen för avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128388198</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>774704</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7156243</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>bladrosetter ca 10 meter utanför gränsen för avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39126-2025 artfynd.xlsx
+++ b/artfynd/A 39126-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/204540</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/378698</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387438</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387495</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387579</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387697</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387693</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387370</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387626</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1718,6 +1768,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1852569</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1823,6 +1878,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387379</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1920,6 +1980,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1951388</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2030,6 +2095,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387390</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2133,6 +2203,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387506</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2239,6 +2314,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388130</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2350,6 +2430,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388139</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2461,8 +2546,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388198</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>